--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.36482876553749</v>
+        <v>2.009284674399843</v>
       </c>
       <c r="D2" t="n">
-        <v>13.35134691444302</v>
+        <v>2.169593873596992</v>
       </c>
       <c r="E2" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F2" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.55986579375906</v>
+        <v>3.665978191485848</v>
       </c>
       <c r="D3" t="n">
-        <v>23.50715328087957</v>
+        <v>3.819912408142931</v>
       </c>
       <c r="E3" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F3" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.82991252058893</v>
+        <v>4.847360784595701</v>
       </c>
       <c r="D4" t="n">
-        <v>31.61056447131298</v>
+        <v>5.13671672658836</v>
       </c>
       <c r="E4" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F4" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.03852981424329</v>
+        <v>4.068761094814535</v>
       </c>
       <c r="D5" t="n">
-        <v>26.39347667837763</v>
+        <v>4.288939960236366</v>
       </c>
       <c r="E5" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F5" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.95573864984193</v>
+        <v>5.355307530599315</v>
       </c>
       <c r="D6" t="n">
-        <v>33.33994801676155</v>
+        <v>5.417741552723752</v>
       </c>
       <c r="E6" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F6" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.79984159782865</v>
+        <v>5.492474259647155</v>
       </c>
       <c r="D7" t="n">
-        <v>23.07054399011865</v>
+        <v>3.748963398394281</v>
       </c>
       <c r="E7" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F7" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.08839589790607</v>
+        <v>2.289364333409736</v>
       </c>
       <c r="D8" t="n">
-        <v>14.26517258659529</v>
+        <v>2.318090545321734</v>
       </c>
       <c r="E8" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F8" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.850080194183434</v>
+        <v>1.600638031554808</v>
       </c>
       <c r="D9" t="n">
-        <v>8.837116961850517</v>
+        <v>1.436031506300709</v>
       </c>
       <c r="E9" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F9" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.26822071450132</v>
+        <v>4.756085866106464</v>
       </c>
       <c r="D10" t="n">
-        <v>29.31872619814481</v>
+        <v>4.764293007198531</v>
       </c>
       <c r="E10" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F10" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.93210744749729</v>
+        <v>4.213967460218311</v>
       </c>
       <c r="D11" t="n">
-        <v>10.73944381737322</v>
+        <v>1.745159620323149</v>
       </c>
       <c r="E11" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F11" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.965588159816</v>
+        <v>5.0319080759701</v>
       </c>
       <c r="D12" t="n">
-        <v>30.82754062401791</v>
+        <v>5.00947535140291</v>
       </c>
       <c r="E12" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F12" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.00454374821522</v>
+        <v>3.575738359084973</v>
       </c>
       <c r="D13" t="n">
-        <v>20.36020120008035</v>
+        <v>3.308532695013056</v>
       </c>
       <c r="E13" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F13" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.16403640518833</v>
+        <v>3.439155915843104</v>
       </c>
       <c r="D14" t="n">
-        <v>19.5674750857443</v>
+        <v>3.179714701433448</v>
       </c>
       <c r="E14" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F14" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.48595865244268</v>
+        <v>3.653968281021936</v>
       </c>
       <c r="D15" t="n">
-        <v>16.1245154965971</v>
+        <v>2.620233768197028</v>
       </c>
       <c r="E15" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F15" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>24.37561856100491</v>
+        <v>3.961038016163297</v>
       </c>
       <c r="D16" t="n">
-        <v>24.01733879218539</v>
+        <v>3.902817553730126</v>
       </c>
       <c r="E16" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F16" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>25.98525582872364</v>
+        <v>4.222604072167591</v>
       </c>
       <c r="D17" t="n">
-        <v>25.68054462471924</v>
+        <v>4.173088501516877</v>
       </c>
       <c r="E17" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F17" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>22.95862289037359</v>
+        <v>3.730776219685708</v>
       </c>
       <c r="D18" t="n">
-        <v>22.51318685044245</v>
+        <v>3.658392863196898</v>
       </c>
       <c r="E18" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F18" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>78.5172753247367</v>
+        <v>12.75905724026971</v>
       </c>
       <c r="D19" t="n">
-        <v>69.64553108419807</v>
+        <v>11.31739880118219</v>
       </c>
       <c r="E19" t="n">
-        <v>14.07871847905899</v>
+        <v>2.287791752847086</v>
       </c>
       <c r="F19" t="n">
-        <v>12.94721758346103</v>
+        <v>2.103922857312417</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
